--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,6 +604,46 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1789457412877</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>120</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,50 @@
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1789974768320</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>18</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ELEMENT 하부 고무 10MM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,46 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1791328623809</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23:17</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="n">
+        <v>120</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,6 +728,46 @@
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1791329299353</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>23:28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="n">
+        <v>120</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,16 +690,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1791328623809</v>
+        <v>1791329299353</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23:17</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -727,46 +727,6 @@
         <v>1</v>
       </c>
       <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1791329299353</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>23:28</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AR-F5203</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>50</v>
-      </c>
-      <c r="H8" t="n">
-        <v>120</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,6 +728,46 @@
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1791330947111</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HP-F8701 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,46 @@
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1791933290609</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>23:14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,123 +690,83 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1791329299353</v>
+        <v>1791330947111</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10블럭</t>
+          <t>7블럭</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AR-F5203</t>
+          <t>HP-F8701 (12"x300#)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>신우</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="I7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1791330947111</v>
+        <v>1791933290609</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7블럭</t>
+          <t>10블럭</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HP-F8701 (12"x300#)</t>
+          <t>AR-F5103A</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>신우</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1791933290609</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>23:14</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" t="n">
-        <v>18</v>
-      </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,46 @@
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1791933552085</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="n">
+        <v>120</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,46 @@
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1791933577496</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,7 +770,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1791933552085</v>
+        <v>1791933577496</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -807,46 +807,6 @@
         <v>1</v>
       </c>
       <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1791933577496</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>23:19</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AR-F5203</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>50</v>
-      </c>
-      <c r="H10" t="n">
-        <v>120</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,46 @@
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1792461062238</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,6 +848,46 @@
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1793142252744</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,6 +888,46 @@
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1793341987223</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" t="n">
+        <v>120</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
